--- a/data/Data_for_figures_4results/Result2_ALLfactors.xlsx
+++ b/data/Data_for_figures_4results/Result2_ALLfactors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\State_SDG\Github\SDG_Interactions-driven-by-Urban_Typologies\data\Data_for_figures_4results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF91548D-1566-495E-ACC2-98790E202F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A18051-82E6-4499-BE62-995B0BA55AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="15648" windowHeight="11316" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="204" yWindow="2688" windowWidth="24372" windowHeight="9024" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
   <si>
     <t xml:space="preserve">num </t>
   </si>
@@ -47,639 +47,321 @@
     <t>city</t>
   </si>
   <si>
-    <t>MSA</t>
-  </si>
-  <si>
     <t>Akron</t>
   </si>
   <si>
-    <t>Akron, OH</t>
-  </si>
-  <si>
     <t>Albany</t>
   </si>
   <si>
-    <t>Albany-Schenectady-Troy, NY</t>
-  </si>
-  <si>
     <t>Albuquerque</t>
   </si>
   <si>
-    <t>Albuquerque, NM</t>
-  </si>
-  <si>
     <t>Allentown</t>
   </si>
   <si>
-    <t>Allentown-Bethlehem-Easton, PA-NJ</t>
-  </si>
-  <si>
     <t>Atlanta</t>
   </si>
   <si>
-    <t>Atlanta-Sandy Springs-Roswell, GA</t>
-  </si>
-  <si>
     <t>Augusta</t>
   </si>
   <si>
-    <t>Augusta-Richmond County, GA-SC</t>
-  </si>
-  <si>
     <t>Austin</t>
   </si>
   <si>
-    <t>Austin-Round Rock, TX</t>
-  </si>
-  <si>
     <t>Bakersfield</t>
   </si>
   <si>
-    <t>Bakersfield, CA</t>
-  </si>
-  <si>
     <t>Baltimore</t>
   </si>
   <si>
-    <t>Baltimore-Columbia-Towson, MD</t>
-  </si>
-  <si>
     <t>Baton Rouge</t>
   </si>
   <si>
-    <t>Baton Rouge, LA</t>
-  </si>
-  <si>
     <t>Birmingham</t>
   </si>
   <si>
-    <t>Birmingham-Hoover, AL</t>
-  </si>
-  <si>
     <t>Boise City</t>
   </si>
   <si>
-    <t>Boise City, ID</t>
-  </si>
-  <si>
     <t>Boston</t>
   </si>
   <si>
-    <t>Boston-Cambridge-Newton, MA-NH</t>
-  </si>
-  <si>
     <t>Bridgeport</t>
   </si>
   <si>
-    <t>Bridgeport-Stamford-Norwalk, CT</t>
-  </si>
-  <si>
     <t>Buffalo</t>
   </si>
   <si>
-    <t>Buffalo-Cheektowaga-Niagara Falls, NY</t>
-  </si>
-  <si>
     <t>Cape Coral</t>
   </si>
   <si>
-    <t>Cape Coral-Fort Myers, FL</t>
-  </si>
-  <si>
     <t>Charleston</t>
   </si>
   <si>
-    <t>Charleston-North Charleston, SC</t>
-  </si>
-  <si>
     <t>Charlotte</t>
   </si>
   <si>
-    <t>Charlotte-Concord-Gastonia, NC-SC</t>
-  </si>
-  <si>
     <t>Chattanooga</t>
   </si>
   <si>
-    <t>Chattanooga, TN-GA</t>
-  </si>
-  <si>
     <t>Chicago</t>
   </si>
   <si>
-    <t>Chicago-Naperville-Elgin, IL-IN-WI</t>
-  </si>
-  <si>
     <t>Cincinnati</t>
   </si>
   <si>
-    <t>Cincinnati, OH-KY-IN</t>
-  </si>
-  <si>
     <t>Cleveland</t>
   </si>
   <si>
-    <t>Cleveland-Elyria, OH</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
-    <t>Colorado Springs, CO</t>
-  </si>
-  <si>
     <t>Columbia</t>
   </si>
   <si>
-    <t>Columbia, SC</t>
-  </si>
-  <si>
     <t>Columbus</t>
   </si>
   <si>
-    <t>Columbus, OH</t>
-  </si>
-  <si>
     <t>Dallas</t>
   </si>
   <si>
-    <t>Dallas-Fort Worth-Arlington, TX</t>
-  </si>
-  <si>
     <t>Dayton</t>
   </si>
   <si>
-    <t>Dayton, OH</t>
-  </si>
-  <si>
     <t>Deltona</t>
   </si>
   <si>
-    <t>Deltona-Daytona Beach-Ormond Beach, FL</t>
-  </si>
-  <si>
     <t>Denver</t>
   </si>
   <si>
-    <t>Denver-Aurora-Lakewood, CO</t>
-  </si>
-  <si>
     <t>Des Moines</t>
   </si>
   <si>
-    <t>Des Moines-West Des Moines, IA</t>
-  </si>
-  <si>
     <t>Detroit</t>
   </si>
   <si>
-    <t>Detroit-Warren-Dearborn, MI</t>
-  </si>
-  <si>
     <t>Durham</t>
   </si>
   <si>
-    <t>Durham-Chapel Hill, NC</t>
-  </si>
-  <si>
     <t>El Paso</t>
   </si>
   <si>
-    <t>El Paso, TX</t>
-  </si>
-  <si>
     <t>Fresno</t>
   </si>
   <si>
-    <t>Fresno, CA</t>
-  </si>
-  <si>
     <t>Grand Rapids</t>
   </si>
   <si>
-    <t>Grand Rapids-Wyoming, MI</t>
-  </si>
-  <si>
     <t>Greensboro</t>
   </si>
   <si>
-    <t>Greensboro-High Point, NC</t>
-  </si>
-  <si>
     <t>Greenville</t>
   </si>
   <si>
-    <t>Greenville-Anderson-Mauldin, SC</t>
-  </si>
-  <si>
     <t>Harrisburg</t>
   </si>
   <si>
-    <t>Harrisburg-Carlisle, PA</t>
-  </si>
-  <si>
     <t>Hartford</t>
   </si>
   <si>
-    <t>Hartford-West Hartford-East Hartford, CT</t>
-  </si>
-  <si>
     <t>Houston</t>
   </si>
   <si>
-    <t>Houston-The Woodlands-Sugar Land, TX</t>
-  </si>
-  <si>
     <t>Indianapolis</t>
   </si>
   <si>
-    <t>Indianapolis-Carmel-Anderson, IN</t>
-  </si>
-  <si>
     <t>Jackson</t>
   </si>
   <si>
-    <t>Jackson, MS</t>
-  </si>
-  <si>
     <t>Jacksonville</t>
   </si>
   <si>
-    <t>Jacksonville, FL</t>
-  </si>
-  <si>
     <t>Kansas City</t>
   </si>
   <si>
-    <t>Kansas City, MO-KS</t>
-  </si>
-  <si>
     <t>Knoxville</t>
   </si>
   <si>
-    <t>Knoxville, TN</t>
-  </si>
-  <si>
     <t>Lakeland</t>
   </si>
   <si>
-    <t>Lakeland-Winter Haven, FL</t>
-  </si>
-  <si>
     <t>Lancaster</t>
   </si>
   <si>
-    <t>Lancaster, PA</t>
-  </si>
-  <si>
     <t>Las Vegas</t>
   </si>
   <si>
-    <t>Las Vegas-Henderson-Paradise, NV</t>
-  </si>
-  <si>
     <t>Little Rock</t>
   </si>
   <si>
-    <t>Little Rock-North Little Rock-Conway, AR</t>
-  </si>
-  <si>
     <t>Los Angeles</t>
   </si>
   <si>
-    <t>Los Angeles-Long Beach-Anaheim, CA</t>
-  </si>
-  <si>
     <t>Louisville</t>
   </si>
   <si>
-    <t>Louisville/Jefferson County, KY-IN</t>
-  </si>
-  <si>
     <t>Madison</t>
   </si>
   <si>
-    <t>Madison, WI</t>
-  </si>
-  <si>
     <t>Manchester</t>
   </si>
   <si>
-    <t>Manchester-Nashua, NH</t>
-  </si>
-  <si>
     <t>McAllen</t>
   </si>
   <si>
-    <t>McAllen-Edinburg-Mission, TX</t>
-  </si>
-  <si>
     <t>Memphis</t>
   </si>
   <si>
-    <t>Memphis, TN-MS-AR</t>
-  </si>
-  <si>
     <t>Miami</t>
   </si>
   <si>
-    <t>Miami-Fort Lauderdale-West Palm Beach, FL</t>
-  </si>
-  <si>
     <t>Milwaukee</t>
   </si>
   <si>
-    <t>Milwaukee-Waukesha-West Allis, WI</t>
-  </si>
-  <si>
     <t>Minneapolis</t>
   </si>
   <si>
-    <t>Minneapolis-St. Paul-Bloomington, MN-WI</t>
-  </si>
-  <si>
     <t>Modesto</t>
   </si>
   <si>
-    <t>Modesto, CA</t>
-  </si>
-  <si>
     <t>Nashville</t>
   </si>
   <si>
-    <t>Nashville-Davidson--Murfreesboro--Franklin, TN</t>
-  </si>
-  <si>
     <t>New Haven</t>
   </si>
   <si>
-    <t>New Haven-Milford, CT</t>
-  </si>
-  <si>
     <t>New Orleans</t>
   </si>
   <si>
-    <t>New Orleans-Metairie, LA</t>
-  </si>
-  <si>
     <t>New York</t>
   </si>
   <si>
-    <t>New York-Newark-Jersey City, NY-NJ-PA</t>
-  </si>
-  <si>
     <t>North Port</t>
   </si>
   <si>
-    <t>North Port-Sarasota-Bradenton, FL</t>
-  </si>
-  <si>
     <t>Ogden</t>
   </si>
   <si>
-    <t>Ogden-Clearfield, UT</t>
-  </si>
-  <si>
     <t>Oklahoma City</t>
   </si>
   <si>
-    <t>Oklahoma City, OK</t>
-  </si>
-  <si>
     <t>Omaha</t>
   </si>
   <si>
-    <t>Omaha-Council Bluffs, NE-IA</t>
-  </si>
-  <si>
     <t>Orlando</t>
   </si>
   <si>
-    <t>Orlando-Kissimmee-Sanford, FL</t>
-  </si>
-  <si>
     <t>Oxnard</t>
   </si>
   <si>
-    <t>Oxnard-Thousand Oaks-Ventura, CA</t>
-  </si>
-  <si>
     <t>Palm Bay</t>
   </si>
   <si>
-    <t>Palm Bay-Melbourne-Titusville, FL</t>
-  </si>
-  <si>
     <t>Philadelphia</t>
   </si>
   <si>
-    <t>Philadelphia-Camden-Wilmington, PA-NJ-DE-MD</t>
-  </si>
-  <si>
     <t>Phoenix</t>
   </si>
   <si>
-    <t>Phoenix-Mesa-Scottsdale, AZ</t>
-  </si>
-  <si>
     <t>Pittsburgh</t>
   </si>
   <si>
-    <t>Pittsburgh, PA</t>
-  </si>
-  <si>
     <t>Portland</t>
   </si>
   <si>
-    <t>Portland-Vancouver-Hillsboro, OR-WA</t>
-  </si>
-  <si>
     <t>Providence</t>
   </si>
   <si>
-    <t>Providence-Warwick, RI-MA</t>
-  </si>
-  <si>
     <t>Provo</t>
   </si>
   <si>
-    <t>Provo-Orem, UT</t>
-  </si>
-  <si>
     <t>Raleigh</t>
   </si>
   <si>
-    <t>Raleigh, NC</t>
-  </si>
-  <si>
     <t>Richmond</t>
   </si>
   <si>
-    <t>Richmond, VA</t>
-  </si>
-  <si>
     <t>Riverside</t>
   </si>
   <si>
-    <t>Riverside-San Bernardino-Ontario, CA</t>
-  </si>
-  <si>
     <t>Rochester</t>
   </si>
   <si>
-    <t>Rochester, NY</t>
-  </si>
-  <si>
     <t>Sacramento</t>
   </si>
   <si>
-    <t>Sacramento--Roseville--Arden-Arcade, CA</t>
-  </si>
-  <si>
     <t>Salt Lake City</t>
   </si>
   <si>
-    <t>Salt Lake City, UT</t>
-  </si>
-  <si>
     <t>San Antonio</t>
   </si>
   <si>
-    <t>San Antonio-New Braunfels, TX</t>
-  </si>
-  <si>
     <t>San Diego</t>
   </si>
   <si>
-    <t>San Diego-Carlsbad, CA</t>
-  </si>
-  <si>
     <t>San Francisco</t>
   </si>
   <si>
-    <t>San Francisco-Oakland-Hayward, CA</t>
-  </si>
-  <si>
     <t>San Jose</t>
   </si>
   <si>
-    <t>San Jose-Sunnyvale-Santa Clara, CA</t>
-  </si>
-  <si>
     <t>Scranton</t>
   </si>
   <si>
-    <t>Scranton--Wilkes-Barre--Hazleton, PA</t>
-  </si>
-  <si>
     <t>Seattle</t>
   </si>
   <si>
-    <t>Seattle-Tacoma-Bellevue, WA</t>
-  </si>
-  <si>
     <t>Spokane</t>
   </si>
   <si>
-    <t>Spokane-Spokane Valley, WA</t>
-  </si>
-  <si>
     <t>Springfield</t>
   </si>
   <si>
-    <t>Springfield, MA</t>
-  </si>
-  <si>
     <t>St. Louis</t>
   </si>
   <si>
-    <t>St. Louis, MO-IL</t>
-  </si>
-  <si>
     <t>Stockton</t>
   </si>
   <si>
-    <t>Stockton-Lodi, CA</t>
-  </si>
-  <si>
     <t>Syracuse</t>
   </si>
   <si>
-    <t>Syracuse, NY</t>
-  </si>
-  <si>
     <t>Tampa</t>
   </si>
   <si>
-    <t>Tampa-St. Petersburg-Clearwater, FL</t>
-  </si>
-  <si>
     <t>Toledo</t>
   </si>
   <si>
-    <t>Toledo, OH</t>
-  </si>
-  <si>
     <t>Trenton</t>
   </si>
   <si>
-    <t>Trenton, NJ</t>
-  </si>
-  <si>
     <t>Tucson</t>
   </si>
   <si>
-    <t>Tucson, AZ</t>
-  </si>
-  <si>
     <t>Tulsa</t>
   </si>
   <si>
-    <t>Tulsa, OK</t>
-  </si>
-  <si>
     <t>Urban Honolulu</t>
   </si>
   <si>
-    <t>Urban Honolulu, HI</t>
-  </si>
-  <si>
     <t>Virginia Beach</t>
   </si>
   <si>
-    <t>Virginia Beach-Norfolk-Newport News, VA-NC</t>
-  </si>
-  <si>
     <t>Washington</t>
   </si>
   <si>
-    <t>Washington-Arlington-Alexandria, DC-VA-MD-WV</t>
-  </si>
-  <si>
     <t>Wichita</t>
   </si>
   <si>
-    <t>Wichita, KS</t>
-  </si>
-  <si>
     <t>Winston</t>
   </si>
   <si>
-    <t>Winston-Salem, NC</t>
-  </si>
-  <si>
     <t>Worcester</t>
   </si>
   <si>
-    <t>Worcester, MA-CT</t>
-  </si>
-  <si>
     <t>Youngstown</t>
   </si>
   <si>
-    <t>Youngstown-Warren-Boardman, OH-PA</t>
-  </si>
-  <si>
     <t>POP density (pop/km2)</t>
   </si>
   <si>
@@ -717,6 +399,9 @@
   </si>
   <si>
     <t>Fed Cor Conv per 100k</t>
+  </si>
+  <si>
+    <t>Cluster</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +723,8 @@
   <dimension ref="A1:P106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="41.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" customWidth="1"/>
     <col min="4" max="4" width="16.109375" customWidth="1"/>
     <col min="5" max="6" width="20.109375" customWidth="1"/>
     <col min="7" max="7" width="12.33203125" customWidth="1"/>
@@ -1047,7 +733,7 @@
     <col min="11" max="12" width="12.6640625" customWidth="1"/>
     <col min="13" max="13" width="23.6640625" customWidth="1"/>
     <col min="14" max="14" width="12.6640625" customWidth="1"/>
-    <col min="15" max="15" width="20.88671875" customWidth="1"/>
+    <col min="15" max="15" width="17.109375" customWidth="1"/>
     <col min="17" max="18" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1059,46 +745,46 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>213</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>220</v>
+        <v>114</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>221</v>
+        <v>115</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>222</v>
+        <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>108</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>218</v>
+        <v>112</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>219</v>
+        <v>113</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>217</v>
+        <v>111</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>225</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -1106,10 +792,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
       </c>
       <c r="D2" s="1">
         <v>301.73044430983902</v>
@@ -1156,10 +842,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>3</v>
       </c>
       <c r="D3" s="1">
         <v>121.69335212716466</v>
@@ -1206,10 +892,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
       </c>
       <c r="D4" s="1">
         <v>37.977776089596567</v>
@@ -1256,10 +942,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3</v>
       </c>
       <c r="D5" s="1">
         <v>223.39370727468443</v>
@@ -1306,10 +992,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>261.54220994857474</v>
@@ -1356,10 +1042,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
       </c>
       <c r="D7" s="1">
         <v>66.621012689490641</v>
@@ -1406,10 +1092,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3</v>
       </c>
       <c r="D8" s="1">
         <v>193.50848353907372</v>
@@ -1456,10 +1142,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
       </c>
       <c r="D9" s="1">
         <v>42.40348978065451</v>
@@ -1506,10 +1192,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
       </c>
       <c r="D10" s="1">
         <v>416.78358494982871</v>
@@ -1556,10 +1242,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
       </c>
       <c r="D11" s="1">
         <v>79.979912982805047</v>
@@ -1606,10 +1292,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
       </c>
       <c r="D12" s="1">
         <v>84.086649009126361</v>
@@ -1656,10 +1342,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
       </c>
       <c r="D13" s="1">
         <v>23.307983932533126</v>
@@ -1706,10 +1392,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
       </c>
       <c r="D14" s="1">
         <v>535.70554312326567</v>
@@ -1756,10 +1442,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
       </c>
       <c r="D15" s="1">
         <v>586.85480488345297</v>
@@ -1806,10 +1492,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
       </c>
       <c r="D16" s="1">
         <v>280.46434242129521</v>
@@ -1856,10 +1542,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
       </c>
       <c r="D17" s="1">
         <v>364.02352450271644</v>
@@ -1906,10 +1592,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
       </c>
       <c r="D18" s="1">
         <v>115.68290662066357</v>
@@ -1956,10 +1642,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
       </c>
       <c r="D19" s="1">
         <v>192.52776431536765</v>
@@ -2006,10 +1692,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
       </c>
       <c r="D20" s="1">
         <v>102.55913563057872</v>
@@ -2056,10 +1742,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3</v>
       </c>
       <c r="D21" s="1">
         <v>511.53607531888616</v>
@@ -2106,10 +1792,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
       </c>
       <c r="D22" s="1">
         <v>202.12372022902713</v>
@@ -2156,10 +1842,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1</v>
       </c>
       <c r="D23" s="1">
         <v>397.61972729552622</v>
@@ -2206,10 +1892,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
       </c>
       <c r="D24" s="1">
         <v>104.13657756636698</v>
@@ -2256,10 +1942,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>50</v>
+        <v>25</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1</v>
       </c>
       <c r="D25" s="1">
         <v>86.021710522413684</v>
@@ -2306,10 +1992,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>52</v>
+        <v>26</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
       </c>
       <c r="D26" s="1">
         <v>167.32749810734546</v>
@@ -2356,10 +2042,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1</v>
       </c>
       <c r="D27" s="1">
         <v>307.93238629105321</v>
@@ -2406,10 +2092,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1</v>
       </c>
       <c r="D28" s="1">
         <v>241.95485034602703</v>
@@ -2456,10 +2142,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>58</v>
+        <v>29</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1</v>
       </c>
       <c r="D29" s="1">
         <v>157.97783769567127</v>
@@ -2506,10 +2192,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>60</v>
+        <v>30</v>
+      </c>
+      <c r="C30" s="1">
+        <v>3</v>
       </c>
       <c r="D30" s="1">
         <v>133.61850756250357</v>
@@ -2556,10 +2242,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>62</v>
+        <v>31</v>
+      </c>
+      <c r="C31" s="1">
+        <v>3</v>
       </c>
       <c r="D31" s="1">
         <v>86.525260862038593</v>
@@ -2606,10 +2292,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>64</v>
+        <v>32</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
       </c>
       <c r="D32" s="1">
         <v>428.17212083441473</v>
@@ -2656,10 +2342,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>66</v>
+        <v>33</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
       </c>
       <c r="D33" s="1">
         <v>124.64057624892394</v>
@@ -2706,10 +2392,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>68</v>
+        <v>34</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2</v>
       </c>
       <c r="D34" s="1">
         <v>58.269365329681726</v>
@@ -2756,10 +2442,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2</v>
       </c>
       <c r="D35" s="1">
         <v>64.106584295320914</v>
@@ -2806,10 +2492,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>72</v>
+        <v>36</v>
+      </c>
+      <c r="C36" s="1">
+        <v>3</v>
       </c>
       <c r="D36" s="1">
         <v>153.17908683089928</v>
@@ -2856,10 +2542,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>74</v>
+        <v>37</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1</v>
       </c>
       <c r="D37" s="1">
         <v>147.41074089261687</v>
@@ -2906,10 +2592,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>76</v>
+        <v>38</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1</v>
       </c>
       <c r="D38" s="1">
         <v>127.60555293330985</v>
@@ -2956,10 +2642,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>78</v>
+        <v>39</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1</v>
       </c>
       <c r="D39" s="1">
         <v>136.13588030896972</v>
@@ -3006,10 +2692,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>80</v>
+        <v>40</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3</v>
       </c>
       <c r="D40" s="1">
         <v>308.48107821367387</v>
@@ -3056,10 +2742,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>82</v>
+        <v>41</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1</v>
       </c>
       <c r="D41" s="1">
         <v>321.95245671182778</v>
@@ -3106,10 +2792,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
       </c>
       <c r="D42" s="1">
         <v>181.73869340260842</v>
@@ -3156,10 +2842,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>86</v>
+        <v>43</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1</v>
       </c>
       <c r="D43" s="1">
         <v>48.080106358624022</v>
@@ -3206,10 +2892,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>88</v>
+        <v>44</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1</v>
       </c>
       <c r="D44" s="1">
         <v>181.46054329304025</v>
@@ -3256,10 +2942,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>90</v>
+        <v>45</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1</v>
       </c>
       <c r="D45" s="1">
         <v>113.17104093295553</v>
@@ -3306,10 +2992,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>92</v>
+        <v>46</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1</v>
       </c>
       <c r="D46" s="1">
         <v>96.820281017013784</v>
@@ -3356,10 +3042,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1</v>
       </c>
       <c r="D47" s="1">
         <v>147.51719648824565</v>
@@ -3406,10 +3092,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>96</v>
+        <v>48</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1</v>
       </c>
       <c r="D48" s="1">
         <v>222.08247479848262</v>
@@ -3456,10 +3142,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>98</v>
+        <v>49</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2</v>
       </c>
       <c r="D49" s="1">
         <v>107.83544447938507</v>
@@ -3506,10 +3192,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1</v>
       </c>
       <c r="D50" s="1">
         <v>69.766711108209662</v>
@@ -3556,10 +3242,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>102</v>
+        <v>51</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2</v>
       </c>
       <c r="D51" s="1">
         <v>1063.295423511343</v>
@@ -3606,10 +3292,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>104</v>
+        <v>52</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1</v>
       </c>
       <c r="D52" s="1">
         <v>139.58429860437417</v>
@@ -3656,10 +3342,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>106</v>
+        <v>53</v>
+      </c>
+      <c r="C53" s="1">
+        <v>3</v>
       </c>
       <c r="D53" s="1">
         <v>76.343353779340944</v>
@@ -3706,10 +3392,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>108</v>
+        <v>54</v>
+      </c>
+      <c r="C54" s="1">
+        <v>3</v>
       </c>
       <c r="D54" s="1">
         <v>180.49249071133224</v>
@@ -3756,10 +3442,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>110</v>
+        <v>55</v>
+      </c>
+      <c r="C55" s="1">
+        <v>2</v>
       </c>
       <c r="D55" s="1">
         <v>211.53684122056438</v>
@@ -3806,10 +3492,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>112</v>
+        <v>56</v>
+      </c>
+      <c r="C56" s="1">
+        <v>1</v>
       </c>
       <c r="D56" s="1">
         <v>104.28669206880406</v>
@@ -3856,10 +3542,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>114</v>
+        <v>57</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2</v>
       </c>
       <c r="D57" s="1">
         <v>469.05540278241511</v>
@@ -3906,10 +3592,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>116</v>
+        <v>58</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1</v>
       </c>
       <c r="D58" s="1">
         <v>418.32648645623652</v>
@@ -3956,10 +3642,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>118</v>
+        <v>59</v>
+      </c>
+      <c r="C59" s="1">
+        <v>3</v>
       </c>
       <c r="D59" s="1">
         <v>182.03842719315199</v>
@@ -4006,10 +3692,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>120</v>
+        <v>60</v>
+      </c>
+      <c r="C60" s="1">
+        <v>2</v>
       </c>
       <c r="D60" s="1">
         <v>141.40662129952005</v>
@@ -4056,10 +3742,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>122</v>
+        <v>61</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1</v>
       </c>
       <c r="D61" s="1">
         <v>116.66711772496114</v>
@@ -4106,10 +3792,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>124</v>
+        <v>62</v>
+      </c>
+      <c r="C62" s="1">
+        <v>3</v>
       </c>
       <c r="D62" s="1">
         <v>549.56915735073699</v>
@@ -4156,10 +3842,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>126</v>
+        <v>63</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1</v>
       </c>
       <c r="D63" s="1">
         <v>153.82871796474419</v>
@@ -4206,10 +3892,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>128</v>
+        <v>64</v>
+      </c>
+      <c r="C64" s="1">
+        <v>3</v>
       </c>
       <c r="D64" s="1">
         <v>946.09623825009419</v>
@@ -4256,10 +3942,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>130</v>
+        <v>65</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1</v>
       </c>
       <c r="D65" s="1">
         <v>239.18584587234989</v>
@@ -4306,10 +3992,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>132</v>
+        <v>66</v>
+      </c>
+      <c r="C66" s="1">
+        <v>3</v>
       </c>
       <c r="D66" s="1">
         <v>35.595218677942448</v>
@@ -4356,10 +4042,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>134</v>
+        <v>67</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1</v>
       </c>
       <c r="D67" s="1">
         <v>96.934016688459309</v>
@@ -4406,10 +4092,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>136</v>
+        <v>68</v>
+      </c>
+      <c r="C68" s="1">
+        <v>3</v>
       </c>
       <c r="D68" s="1">
         <v>82.920937762296148</v>
@@ -4456,10 +4142,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>138</v>
+        <v>69</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1</v>
       </c>
       <c r="D69" s="1">
         <v>278.36094335637557</v>
@@ -4506,10 +4192,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>140</v>
+        <v>70</v>
+      </c>
+      <c r="C70" s="1">
+        <v>3</v>
       </c>
       <c r="D70" s="1">
         <v>178.95847934862843</v>
@@ -4556,10 +4242,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>142</v>
+        <v>71</v>
+      </c>
+      <c r="C71" s="1">
+        <v>1</v>
       </c>
       <c r="D71" s="1">
         <v>224.07272243121065</v>
@@ -4606,10 +4292,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>144</v>
+        <v>72</v>
+      </c>
+      <c r="C72" s="1">
+        <v>3</v>
       </c>
       <c r="D72" s="1">
         <v>511.39565281454998</v>
@@ -4656,10 +4342,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>146</v>
+        <v>73</v>
+      </c>
+      <c r="C73" s="1">
+        <v>2</v>
       </c>
       <c r="D73" s="1">
         <v>125.57926200792653</v>
@@ -4706,10 +4392,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>148</v>
+        <v>74</v>
+      </c>
+      <c r="C74" s="1">
+        <v>3</v>
       </c>
       <c r="D74" s="1">
         <v>170.58160025598809</v>
@@ -4756,10 +4442,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>150</v>
+        <v>75</v>
+      </c>
+      <c r="C75" s="1">
+        <v>3</v>
       </c>
       <c r="D75" s="1">
         <v>141.55774388752863</v>
@@ -4806,10 +4492,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>152</v>
+        <v>76</v>
+      </c>
+      <c r="C76" s="1">
+        <v>3</v>
       </c>
       <c r="D76" s="1">
         <v>394.38955710620945</v>
@@ -4856,10 +4542,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>154</v>
+        <v>77</v>
+      </c>
+      <c r="C77" s="1">
+        <v>3</v>
       </c>
       <c r="D77" s="1">
         <v>44.202962934557071</v>
@@ -4906,10 +4592,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>156</v>
+        <v>78</v>
+      </c>
+      <c r="C78" s="1">
+        <v>3</v>
       </c>
       <c r="D78" s="1">
         <v>243.4026715961638</v>
@@ -4956,10 +4642,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>158</v>
+        <v>79</v>
+      </c>
+      <c r="C79" s="1">
+        <v>1</v>
       </c>
       <c r="D79" s="1">
         <v>109.83751789582472</v>
@@ -5006,10 +4692,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>160</v>
+        <v>80</v>
+      </c>
+      <c r="C80" s="1">
+        <v>2</v>
       </c>
       <c r="D80" s="1">
         <v>64.87037314453876</v>
@@ -5056,10 +4742,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>162</v>
+        <v>81</v>
+      </c>
+      <c r="C81" s="1">
+        <v>1</v>
       </c>
       <c r="D81" s="1">
         <v>127.42337434095155</v>
@@ -5106,10 +4792,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>164</v>
+        <v>82</v>
+      </c>
+      <c r="C82" s="1">
+        <v>2</v>
       </c>
       <c r="D82" s="1">
         <v>176.19657301409379</v>
@@ -5156,10 +4842,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>166</v>
+        <v>83</v>
+      </c>
+      <c r="C83" s="1">
+        <v>3</v>
       </c>
       <c r="D83" s="1">
         <v>60.45300005587962</v>
@@ -5206,10 +4892,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>168</v>
+        <v>84</v>
+      </c>
+      <c r="C84" s="1">
+        <v>2</v>
       </c>
       <c r="D84" s="1">
         <v>130.6222757838832</v>
@@ -5256,10 +4942,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>170</v>
+        <v>85</v>
+      </c>
+      <c r="C85" s="1">
+        <v>3</v>
       </c>
       <c r="D85" s="1">
         <v>306.24369828411545</v>
@@ -5306,10 +4992,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>172</v>
+        <v>86</v>
+      </c>
+      <c r="C86" s="1">
+        <v>3</v>
       </c>
       <c r="D86" s="1">
         <v>738.86348799087727</v>
@@ -5356,10 +5042,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>174</v>
+        <v>87</v>
+      </c>
+      <c r="C87" s="1">
+        <v>3</v>
       </c>
       <c r="D87" s="1">
         <v>287.92982728617204</v>
@@ -5406,10 +5092,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>176</v>
+        <v>88</v>
+      </c>
+      <c r="C88" s="1">
+        <v>1</v>
       </c>
       <c r="D88" s="1">
         <v>122.79463485141791</v>
@@ -5456,10 +5142,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>178</v>
+        <v>89</v>
+      </c>
+      <c r="C89" s="1">
+        <v>3</v>
       </c>
       <c r="D89" s="1">
         <v>254.36246635827453</v>
@@ -5506,10 +5192,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>180</v>
+        <v>90</v>
+      </c>
+      <c r="C90" s="1">
+        <v>2</v>
       </c>
       <c r="D90" s="1">
         <v>38.619635712334706</v>
@@ -5556,10 +5242,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>182</v>
+        <v>91</v>
+      </c>
+      <c r="C91" s="1">
+        <v>3</v>
       </c>
       <c r="D91" s="1">
         <v>213.13292069664081</v>
@@ -5606,10 +5292,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>184</v>
+        <v>92</v>
+      </c>
+      <c r="C92" s="1">
+        <v>1</v>
       </c>
       <c r="D92" s="1">
         <v>137.83680872030578</v>
@@ -5656,10 +5342,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>186</v>
+        <v>93</v>
+      </c>
+      <c r="C93" s="1">
+        <v>2</v>
       </c>
       <c r="D93" s="1">
         <v>206.7067628992821</v>
@@ -5706,10 +5392,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>188</v>
+        <v>94</v>
+      </c>
+      <c r="C94" s="1">
+        <v>1</v>
       </c>
       <c r="D94" s="1">
         <v>106.01536440168086</v>
@@ -5756,10 +5442,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>190</v>
+        <v>95</v>
+      </c>
+      <c r="C95" s="1">
+        <v>1</v>
       </c>
       <c r="D95" s="1">
         <v>474.65495958076491</v>
@@ -5806,10 +5492,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>192</v>
+        <v>96</v>
+      </c>
+      <c r="C96" s="1">
+        <v>1</v>
       </c>
       <c r="D96" s="1">
         <v>170.92696766030897</v>
@@ -5856,10 +5542,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>194</v>
+        <v>97</v>
+      </c>
+      <c r="C97" s="1">
+        <v>3</v>
       </c>
       <c r="D97" s="1">
         <v>644.88331383919103</v>
@@ -5906,10 +5592,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>196</v>
+        <v>98</v>
+      </c>
+      <c r="C98" s="1">
+        <v>2</v>
       </c>
       <c r="D98" s="1">
         <v>42.982898726384647</v>
@@ -5956,10 +5642,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>198</v>
+        <v>99</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1</v>
       </c>
       <c r="D99" s="1">
         <v>61.013963086401397</v>
@@ -6006,10 +5692,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>200</v>
+        <v>100</v>
+      </c>
+      <c r="C100" s="1">
+        <v>3</v>
       </c>
       <c r="D100" s="1">
         <v>635.55028826482112</v>
@@ -6056,10 +5742,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>202</v>
+        <v>101</v>
+      </c>
+      <c r="C101" s="1">
+        <v>1</v>
       </c>
       <c r="D101" s="1">
         <v>248.1669717920295</v>
@@ -6106,10 +5792,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>204</v>
+        <v>102</v>
+      </c>
+      <c r="C102" s="1">
+        <v>3</v>
       </c>
       <c r="D102" s="1">
         <v>384.22574662449045</v>
@@ -6156,10 +5842,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>206</v>
+        <v>103</v>
+      </c>
+      <c r="C103" s="1">
+        <v>1</v>
       </c>
       <c r="D103" s="1">
         <v>49.805623962157654</v>
@@ -6206,10 +5892,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>208</v>
+        <v>104</v>
+      </c>
+      <c r="C104" s="1">
+        <v>1</v>
       </c>
       <c r="D104" s="1">
         <v>128.35522529322685</v>
@@ -6256,10 +5942,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>210</v>
+        <v>105</v>
+      </c>
+      <c r="C105" s="1">
+        <v>3</v>
       </c>
       <c r="D105" s="1">
         <v>179.83382655679264</v>
@@ -6306,10 +5992,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>212</v>
+        <v>106</v>
+      </c>
+      <c r="C106" s="1">
+        <v>1</v>
       </c>
       <c r="D106" s="1">
         <v>122.92162069456097</v>
